--- a/output/pdf_financials_xlsx/OAM.xlsx
+++ b/output/pdf_financials_xlsx/OAM.xlsx
@@ -3396,10 +3396,10 @@
         <v>0.091907</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>6.885</v>
+        <v>7.506</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>8.914</v>
+        <v>9.535</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>9.686999999999999</v>
@@ -3408,7 +3408,7 @@
         <v>10.36</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>9.926</v>
+        <v>10.368</v>
       </c>
     </row>
     <row r="93">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6043,7 +6043,11 @@
           <t>Warrant Reserve 11</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -8090,7 +8094,11 @@
           <t>Warrants reserve 11</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -9110,7 +9118,11 @@
           <t>Warrants reserve 12</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/OAM.xlsx
+++ b/output/pdf_financials_xlsx/OAM.xlsx
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.875224</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>29.577</v>
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.875224</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>29.577</v>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">

--- a/output/pdf_financials_xlsx/OAM.xlsx
+++ b/output/pdf_financials_xlsx/OAM.xlsx
@@ -3611,16 +3611,16 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.758</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.855</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.399</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>1.069</v>
       </c>
       <c r="H100" s="3" t="n">
         <v>0</v>
@@ -3971,10 +3971,10 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.442</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.505</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -12077,7 +12077,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -12722,7 +12722,11 @@
           <t>Proceeds from disposal of property and equipment 5</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -13328,7 +13332,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -14438,7 +14442,11 @@
           <t>Proceeds from disposal of property and equipment 6</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/OAM.xlsx
+++ b/output/pdf_financials_xlsx/OAM.xlsx
@@ -3701,19 +3701,19 @@
         <v>0</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.249</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-1.251</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>-0.109</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>0.701</v>
       </c>
     </row>
     <row r="104">
@@ -3797,13 +3797,13 @@
         <v>-1.694</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>1.23</v>
+        <v>1.424</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.99</v>
+        <v>-1.099</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>3.566</v>
+        <v>4.267</v>
       </c>
     </row>
     <row r="107">
@@ -4091,19 +4091,19 @@
         <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.058</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.014</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.008</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.025</v>
       </c>
     </row>
     <row r="117">
@@ -10991,7 +10991,11 @@
           <t>Decrease (increase) in prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -11528,7 +11532,11 @@
           <t>Purchase of intangible assets 4</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -12881,7 +12889,11 @@
           <t>Purchase of intangible assets 4</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -13738,7 +13750,11 @@
           <t>Increase in prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -14544,7 +14560,11 @@
           <t>Purchase of intangible assets 5</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
